--- a/TMC_Vision_Accuracy_Summary.xlsx
+++ b/TMC_Vision_Accuracy_Summary.xlsx
@@ -575,7 +575,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Baseline Data'!$A$2:$A$49</f>
+              <f>'Baseline Data'!$B$2:$B$49</f>
             </numRef>
           </cat>
           <val>
@@ -800,7 +800,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Calibration1 Data'!$A$2:$A$48</f>
+              <f>'Calibration1 Data'!$B$2:$B$48</f>
             </numRef>
           </cat>
           <val>
